--- a/docs/source/_extra/case_template.xlsx
+++ b/docs/source/_extra/case_template.xlsx
@@ -17,9 +17,10 @@
     <sheet name="Photos" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Connections" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Openings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="MasonryTypes" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Measured" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="_lists" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet name="Vulnerabilities" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="MasonryTypes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Measured" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="_lists" sheetId="14" state="hidden" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -258,122 +259,17 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Name, the same as the IFC material</t>
+        <t>Facade whose wall has it</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Description</t>
+        <t>FMO vulnerability</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: unit dimensions</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: unit shape</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: unit material</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: mortar quality</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: horizontal joints</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: vertical joints</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: wall connections</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for unit dimensions</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for unit shape</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for unit material</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for mortar quality</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for horizontal joints</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for vertical joints</t>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for wall connections</t>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
-      <text>
-        <t>General evidence (optional)</t>
-      </text>
-    </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
-      <text>
-        <t>Assumptions and caveats, one per line</t>
-      </text>
-    </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
-      <text>
-        <t>Mass density (HMO has no rule for it)</t>
-      </text>
-    </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
-      <text>
-        <t>Source of the density</t>
-      </text>
-    </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
-      <text>
-        <t>Code category it is compared with (optional)</t>
-      </text>
-    </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
-      <text>
-        <t>Note on the comparison (optional)</t>
-      </text>
-    </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
-      <text>
-        <t>Lower variant, as parameter=value; ... (optional)</t>
-      </text>
-    </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
-      <text>
-        <t>Upper variant, as parameter=value; ... (optional)</t>
+        <t>What shows it, and its source</t>
       </text>
     </comment>
   </commentList>
@@ -381,6 +277,136 @@
 </file>
 
 <file path=xl/comments/comment12.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>openBIMtoFEM</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Name, the same as the IFC material</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Description</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: unit dimensions</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: unit shape</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: unit material</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: mortar quality</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: horizontal joints</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: vertical joints</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: wall connections</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for unit dimensions</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for unit shape</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for unit material</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for mortar quality</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for horizontal joints</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for vertical joints</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for wall connections</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>General evidence (optional)</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>Assumptions and caveats, one per line</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>Mass density (HMO has no rule for it)</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>Source of the density</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>Code category it is compared with (optional)</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Note on the comparison (optional)</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
+      <text>
+        <t>Lower variant, as parameter=value; ... (optional)</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
+        <t>Upper variant, as parameter=value; ... (optional)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>openBIMtoFEM</author>
@@ -1181,6 +1207,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>facade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>vulnerability</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=_lists!$L$2:$L$9</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1361,7 +1429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1410,13 +1478,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1475,6 +1543,11 @@
           <t>yes/no</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>vulnerability</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1532,6 +1605,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1589,6 +1667,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1641,6 +1724,11 @@
           <t>Tie</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -1663,6 +1751,11 @@
           <t>Document</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="C6" t="inlineStr">
@@ -1675,6 +1768,11 @@
           <t>Publication</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="C7" t="inlineStr">
@@ -1687,6 +1785,11 @@
           <t>BuildingInformationModel</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ExcessiveSlenderness</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="C8" t="inlineStr">
@@ -1694,11 +1797,21 @@
           <t>squared_hard_stone</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>OpeningsNearIntersections</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
           <t>irregular_hard_stone</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PresenceOfHorizontalThrust</t>
         </is>
       </c>
     </row>

--- a/docs/source/_extra/case_template.xlsx
+++ b/docs/source/_extra/case_template.xlsx
@@ -670,6 +670,11 @@
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>Name of its masonry type (MasonryTypes)</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>GlobalIds of its IFC elements, separated by ; (set by the editor)</t>
       </text>
     </comment>
   </commentList>
@@ -2120,13 +2125,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2148,6 +2154,11 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masonry_type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>elements</t>
         </is>
       </c>
     </row>

--- a/docs/source/_extra/case_template.xlsx
+++ b/docs/source/_extra/case_template.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Project" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Organisations" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="People" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Activities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Documents" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Units" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Facades" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Photos" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Connections" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Openings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Vulnerabilities" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="MasonryTypes" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Measured" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="_lists" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organisations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Activities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facades" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Photos" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connections" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Openings" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vulnerabilities" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MasonryTypes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Measured" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="14" state="hidden" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -294,37 +294,37 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: unit dimensions</t>
+        <t>Morphological characteristic: unit dimensions</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: unit shape</t>
+        <t>Morphological characteristic: unit shape</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: unit material</t>
+        <t>Morphological characteristic: unit material</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: mortar quality</t>
+        <t>Morphological characteristic: mortar quality</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: horizontal joints</t>
+        <t>Morphological characteristic: horizontal joints</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: vertical joints</t>
+        <t>Morphological characteristic: vertical joints</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: wall connections</t>
+        <t>Morphological characteristic: wall connections</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
@@ -394,12 +394,12 @@
     </comment>
     <comment ref="W1" authorId="0" shapeId="0">
       <text>
-        <t>Lower variant, as parameter=value; ... (optional)</t>
+        <t>Lower variant, as characteristic=category; ... (optional)</t>
       </text>
     </comment>
     <comment ref="X1" authorId="0" shapeId="0">
       <text>
-        <t>Upper variant, as parameter=value; ... (optional)</t>
+        <t>Upper variant, as characteristic=category; ... (optional)</t>
       </text>
     </comment>
   </commentList>
@@ -1239,7 +1239,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$L$2:$L$9</formula1>
     </dataValidation>
   </dataValidations>
@@ -1407,25 +1407,25 @@
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$C$2:$C$9</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$D$2:$D$5</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$E$2:$E$4</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$F$2:$F$4</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$G$2:$G$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -2047,7 +2047,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$H$2:$H$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -2107,10 +2107,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$I$2:$I$4</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$K$2:$K$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -2286,7 +2286,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$J$2:$J$4</formula1>
     </dataValidation>
   </dataValidations>
